--- a/芯片测试数据.xlsx
+++ b/芯片测试数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="12560"/>
+    <workbookView windowWidth="28000" windowHeight="13160"/>
   </bookViews>
   <sheets>
     <sheet name="芯片信息" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="152">
   <si>
     <t>序号</t>
   </si>
@@ -41,10 +41,262 @@
     <t>组号</t>
   </si>
   <si>
+    <t>00000301</t>
+  </si>
+  <si>
+    <t>芯片组1</t>
+  </si>
+  <si>
+    <t>00000302</t>
+  </si>
+  <si>
+    <t>00000303</t>
+  </si>
+  <si>
+    <t>00000304</t>
+  </si>
+  <si>
+    <t>00000305</t>
+  </si>
+  <si>
+    <t>00000306</t>
+  </si>
+  <si>
+    <t>00000307</t>
+  </si>
+  <si>
+    <t>00000308</t>
+  </si>
+  <si>
+    <t>00000309</t>
+  </si>
+  <si>
+    <t>00000310</t>
+  </si>
+  <si>
+    <t>00000311</t>
+  </si>
+  <si>
+    <t>00000312</t>
+  </si>
+  <si>
+    <t>00000313</t>
+  </si>
+  <si>
+    <t>00000314</t>
+  </si>
+  <si>
+    <t>00000315</t>
+  </si>
+  <si>
+    <t>00000316</t>
+  </si>
+  <si>
+    <t>00000317</t>
+  </si>
+  <si>
+    <t>00000318</t>
+  </si>
+  <si>
+    <t>00000319</t>
+  </si>
+  <si>
+    <t>00000320</t>
+  </si>
+  <si>
+    <t>00000401</t>
+  </si>
+  <si>
+    <t>芯片组2</t>
+  </si>
+  <si>
+    <t>00000402</t>
+  </si>
+  <si>
+    <t>00000403</t>
+  </si>
+  <si>
+    <t>00000404</t>
+  </si>
+  <si>
+    <t>00000405</t>
+  </si>
+  <si>
+    <t>00000406</t>
+  </si>
+  <si>
+    <t>00000407</t>
+  </si>
+  <si>
+    <t>00000408</t>
+  </si>
+  <si>
+    <t>00000409</t>
+  </si>
+  <si>
+    <t>00000410</t>
+  </si>
+  <si>
+    <t>00000411</t>
+  </si>
+  <si>
+    <t>00000412</t>
+  </si>
+  <si>
+    <t>00000413</t>
+  </si>
+  <si>
+    <t>00000414</t>
+  </si>
+  <si>
+    <t>00000415</t>
+  </si>
+  <si>
+    <t>00000416</t>
+  </si>
+  <si>
+    <t>00000417</t>
+  </si>
+  <si>
+    <t>00000418</t>
+  </si>
+  <si>
+    <t>00000419</t>
+  </si>
+  <si>
+    <t>00000420</t>
+  </si>
+  <si>
+    <t>00000501</t>
+  </si>
+  <si>
+    <t>芯片组3</t>
+  </si>
+  <si>
+    <t>00000502</t>
+  </si>
+  <si>
+    <t>00000503</t>
+  </si>
+  <si>
+    <t>00000504</t>
+  </si>
+  <si>
+    <t>00000505</t>
+  </si>
+  <si>
+    <t>00000506</t>
+  </si>
+  <si>
+    <t>00000507</t>
+  </si>
+  <si>
+    <t>00000508</t>
+  </si>
+  <si>
+    <t>00000509</t>
+  </si>
+  <si>
+    <t>00000510</t>
+  </si>
+  <si>
+    <t>00000511</t>
+  </si>
+  <si>
+    <t>00000512</t>
+  </si>
+  <si>
+    <t>00000513</t>
+  </si>
+  <si>
+    <t>00000514</t>
+  </si>
+  <si>
+    <t>00000515</t>
+  </si>
+  <si>
+    <t>00000516</t>
+  </si>
+  <si>
+    <t>00000517</t>
+  </si>
+  <si>
+    <t>00000518</t>
+  </si>
+  <si>
+    <t>00000519</t>
+  </si>
+  <si>
+    <t>00000520</t>
+  </si>
+  <si>
+    <t>00000601</t>
+  </si>
+  <si>
+    <t>芯片组4</t>
+  </si>
+  <si>
+    <t>00000602</t>
+  </si>
+  <si>
+    <t>00000603</t>
+  </si>
+  <si>
+    <t>00000604</t>
+  </si>
+  <si>
+    <t>00000605</t>
+  </si>
+  <si>
+    <t>00000606</t>
+  </si>
+  <si>
+    <t>00000607</t>
+  </si>
+  <si>
+    <t>00000608</t>
+  </si>
+  <si>
+    <t>00000609</t>
+  </si>
+  <si>
+    <t>00000610</t>
+  </si>
+  <si>
+    <t>00000611</t>
+  </si>
+  <si>
+    <t>00000612</t>
+  </si>
+  <si>
+    <t>00000613</t>
+  </si>
+  <si>
+    <t>00000614</t>
+  </si>
+  <si>
+    <t>00000615</t>
+  </si>
+  <si>
+    <t>00000616</t>
+  </si>
+  <si>
+    <t>00000617</t>
+  </si>
+  <si>
+    <t>00000618</t>
+  </si>
+  <si>
+    <t>00000619</t>
+  </si>
+  <si>
+    <t>00000620</t>
+  </si>
+  <si>
     <t>00000701</t>
   </si>
   <si>
-    <t>分组1</t>
+    <t>芯片组5</t>
   </si>
   <si>
     <t>00000702</t>
@@ -107,7 +359,7 @@
     <t>00000801</t>
   </si>
   <si>
-    <t>分组2</t>
+    <t>芯片组6</t>
   </si>
   <si>
     <t>00000802</t>
@@ -170,7 +422,7 @@
     <t>00000901</t>
   </si>
   <si>
-    <t>分组3</t>
+    <t>芯片组7</t>
   </si>
   <si>
     <t>00000902</t>
@@ -230,67 +482,7 @@
     <t>00000920</t>
   </si>
   <si>
-    <t>00000601</t>
-  </si>
-  <si>
-    <t>分组4</t>
-  </si>
-  <si>
-    <t>00000602</t>
-  </si>
-  <si>
-    <t>00000603</t>
-  </si>
-  <si>
-    <t>00000604</t>
-  </si>
-  <si>
-    <t>00000605</t>
-  </si>
-  <si>
-    <t>00000606</t>
-  </si>
-  <si>
-    <t>00000607</t>
-  </si>
-  <si>
-    <t>00000608</t>
-  </si>
-  <si>
-    <t>00000609</t>
-  </si>
-  <si>
-    <t>00000610</t>
-  </si>
-  <si>
-    <t>00000611</t>
-  </si>
-  <si>
-    <t>00000612</t>
-  </si>
-  <si>
-    <t>00000613</t>
-  </si>
-  <si>
-    <t>00000614</t>
-  </si>
-  <si>
-    <t>00000615</t>
-  </si>
-  <si>
-    <t>00000616</t>
-  </si>
-  <si>
-    <t>00000617</t>
-  </si>
-  <si>
-    <t>00000618</t>
-  </si>
-  <si>
-    <t>00000619</t>
-  </si>
-  <si>
-    <t>00000620</t>
+    <t>00000921</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1455,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2406,6 +2598,860 @@
         <v>68</v>
       </c>
     </row>
+    <row r="82" spans="1:4">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>701</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D82" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>702</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D83" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>703</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D84" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>704</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D85" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>705</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D86" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>706</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D87" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>707</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D88" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>708</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>709</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D90" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>710</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>711</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D92" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>712</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D93" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>713</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D94" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>714</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D95" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>715</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D96" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>716</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D97" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>717</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D98" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>718</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D99" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>719</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D100" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>720</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D101" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>801</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>802</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D103" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>803</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D104" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>804</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D105" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>805</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D106" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>806</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D107" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>807</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D108" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>808</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D109" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>809</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D110" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>810</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>811</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D112" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>812</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D113" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>813</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D114" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>814</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D115" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>815</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D116" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>816</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D117" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>817</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D118" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>818</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D119" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>819</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D120" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>820</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D121" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>901</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D122" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>902</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D123" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>903</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D124" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>904</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D125" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>905</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D126" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>906</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D127" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>907</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D128" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>908</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D129" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>909</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D130" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>910</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D131" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>911</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D132" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>912</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D133" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>913</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D134" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>914</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D135" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>915</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D136" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>916</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D137" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>917</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D138" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>918</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D139" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>919</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D140" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>920</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D141" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>921</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D142" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
